--- a/execl/装备表.xlsx
+++ b/execl/装备表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\godot_object\2D\Godot-Collaboration-Project\execl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CA10A2-B36C-4E13-BE4E-273C201277AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="备注_表格关系说明" sheetId="5" r:id="rId1"/>
@@ -14,24 +20,11 @@
     <sheet name="套装" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="130">
   <si>
     <t>表格ID</t>
   </si>
@@ -299,18 +292,164 @@
   <si>
     <t>元素使</t>
   </si>
+  <si>
+    <t>eq_mage_weapon_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>见习法杖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ico_eq_wuqi01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8|12</t>
+  </si>
+  <si>
+    <t>res://assets/texture/all_icon.png</t>
+  </si>
+  <si>
+    <t>eq_mage_head_01</t>
+  </si>
+  <si>
+    <t>学徒尖帽</t>
+  </si>
+  <si>
+    <t>ico_eq_toukui01</t>
+  </si>
+  <si>
+    <t>Helmet</t>
+  </si>
+  <si>
+    <t>18|24</t>
+  </si>
+  <si>
+    <t>eq_mage_armor_01</t>
+  </si>
+  <si>
+    <t>布纹法袍</t>
+  </si>
+  <si>
+    <t>ico_eq_yifu01</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>28|36</t>
+  </si>
+  <si>
+    <t>2,100|5,50</t>
+  </si>
+  <si>
+    <t>eq_mage_gloves_01</t>
+  </si>
+  <si>
+    <t>导能护手</t>
+  </si>
+  <si>
+    <t>ico_eq_shoutao01</t>
+  </si>
+  <si>
+    <t>Gloves</t>
+  </si>
+  <si>
+    <t>4|6</t>
+  </si>
+  <si>
+    <t>eq_mage_pants_01</t>
+  </si>
+  <si>
+    <t>行路长裤</t>
+  </si>
+  <si>
+    <t>ico_eq_kuzi01</t>
+  </si>
+  <si>
+    <t>Pants</t>
+  </si>
+  <si>
+    <t>20|26</t>
+  </si>
+  <si>
+    <t>eq_mage_shoes_01</t>
+  </si>
+  <si>
+    <t>轻羽短靴</t>
+  </si>
+  <si>
+    <t>ico_eq_xiezi01</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t>eq_mage_ring_01</t>
+  </si>
+  <si>
+    <t>静心水戒</t>
+  </si>
+  <si>
+    <t>ico_eq_jiezhi01</t>
+  </si>
+  <si>
+    <t>Bracelet</t>
+  </si>
+  <si>
+    <t>6|10</t>
+  </si>
+  <si>
+    <t>eq_mage_neck_01</t>
+  </si>
+  <si>
+    <t>辉石项链</t>
+  </si>
+  <si>
+    <t>ico_eq_xianglian01</t>
+  </si>
+  <si>
+    <t>Necklace</t>
+  </si>
+  <si>
+    <t>22|30</t>
+  </si>
+  <si>
+    <t>eq_mage_artifact_01</t>
+  </si>
+  <si>
+    <t>古代护符</t>
+  </si>
+  <si>
+    <t>ico_eq_hufu01</t>
+  </si>
+  <si>
+    <t>Earrings</t>
+  </si>
+  <si>
+    <t>10|14</t>
+  </si>
+  <si>
+    <t>14|18</t>
+  </si>
+  <si>
+    <t>1,100|2,100</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,351 +464,27 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -692,275 +507,30 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -968,66 +538,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2 7" xfId="49"/>
+    <cellStyle name="常规 2 7" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1277,39 +803,38 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="19.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="20.375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="8.375" style="8" customWidth="1"/>
-    <col min="7" max="8" width="10.625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="18.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="10.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.375" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="16" style="1" customWidth="1"/>
@@ -1317,7 +842,7 @@
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1335,7 +860,7 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1351,7 +876,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1359,15 +884,15 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" ht="128.25" spans="1:12">
+    <row r="4" spans="1:17" ht="128.25" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1394,14 +919,14 @@
       <c r="J4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1439,7 +964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1477,7 +1002,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -1493,13 +1018,13 @@
       <c r="E7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -1515,7 +1040,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -1553,14 +1078,14 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -1585,25 +1110,396 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1100</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1100</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2100</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N11" s="1">
+        <v>16</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="1">
+        <v>32</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="7">
+        <v>6100</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N13" s="1">
+        <v>48</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="7">
+        <v>5100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N14" s="1">
+        <v>64</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="7">
+        <v>6100</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N15" s="1">
+        <v>80</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="7">
+        <v>6100</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N16" s="1">
+        <v>96</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="7">
+        <v>5100</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N17" s="1">
+        <v>112</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N18" s="1">
+        <v>128</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="6" customWidth="1"/>
-    <col min="2" max="6" width="12.875" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="13.75" style="5" customWidth="1"/>
+    <col min="2" max="6" width="12.875" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1614,34 +1510,34 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="7"/>
+      <c r="C2" s="6"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" ht="44" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" ht="44.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" ht="42.75" spans="1:6">
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="7"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="4" t="s">
         <v>52</v>
       </c>
@@ -1650,14 +1546,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1668,14 +1564,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1688,32 +1584,32 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="4" t="s">
         <v>40</v>
       </c>
@@ -1724,212 +1620,211 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="10" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.5" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1939,45 +1834,45 @@
       <c r="D1" s="2"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="6"/>
       <c r="D2" s="2"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="7"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" ht="28.5" spans="1:5">
+    <row r="4" spans="1:5" ht="28.5" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="7"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="2"/>
       <c r="E4" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1985,14 +1880,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2002,14 +1897,14 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="2" t="s">
         <v>66</v>
       </c>
@@ -2017,14 +1912,14 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2032,191 +1927,190 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
-      <c r="C22" s="7"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
-      <c r="C23" s="7"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="7"/>
+      <c r="C24" s="6"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="7"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="7"/>
+      <c r="C26" s="6"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
-      <c r="C28" s="7"/>
+      <c r="C28" s="6"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
-      <c r="C29" s="7"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.75" style="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="1"/>
@@ -2225,7 +2119,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2236,7 +2130,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2245,7 +2139,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -2254,7 +2148,7 @@
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
@@ -2263,7 +2157,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -2280,7 +2174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -2297,7 +2191,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -2314,7 +2208,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2331,151 +2225,151 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="5"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="5"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2483,7 +2377,7 @@
       <c r="E29" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>